--- a/Balibago_traci/batch_results/BP_A2C_Results.xlsx
+++ b/Balibago_traci/batch_results/BP_A2C_Results.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30 Runs  |  10 Normal  •  10 Slow  •  10 Jam  |  A2C trained model (test mode)</t>
+          <t>30 Runs  |  10 Normal  •  10 Slow  •  10 Jam  |  A2C baseline (integrated loop)</t>
         </is>
       </c>
     </row>
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>97.8454</v>
+        <v>94.8857</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>140.2024</v>
+        <v>140.0585</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.1168</v>
+        <v>2.1784</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1274.3294</v>
+        <v>1284.9805</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>3.1091</v>
+        <v>411.4067</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.5291</v>
+        <v>16.7324</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>98.62479999999999</v>
+        <v>97.9868</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>178.0798</v>
+        <v>178.5107</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.0089</v>
+        <v>2.0763</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1207.3171</v>
+        <v>1206.5244</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>2.8815</v>
+        <v>374.7543</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6128</v>
+        <v>17.5669</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -689,22 +689,22 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>96.69929999999999</v>
+        <v>96.13800000000001</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>190.3748</v>
+        <v>184.8034</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1.7794</v>
+        <v>1.7899</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1166.044</v>
+        <v>1172.2541</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2.5842</v>
+        <v>329.67</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4916</v>
+        <v>12.0481</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>97.7427</v>
+        <v>97.8151</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>169.5542</v>
+        <v>159.3791</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1.8943</v>
+        <v>1.9607</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1207.2233</v>
+        <v>1229.8463</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2.7288</v>
+        <v>348.6787</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5593</v>
+        <v>14.8906</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -739,22 +739,22 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>97.5719</v>
+        <v>119.9532</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>158.4057</v>
+        <v>151.7341</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1.8861</v>
+        <v>2.212</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1196.8944</v>
+        <v>1310.7181</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2.7977</v>
+        <v>381.1924</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.4276</v>
+        <v>15.2808</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>98.7174</v>
+        <v>95.4683</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>168.8274</v>
+        <v>154.6477</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1.9375</v>
+        <v>1.8746</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1171.6813</v>
+        <v>1187.5336</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>2.778</v>
+        <v>350.2554</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.5927</v>
+        <v>15.3081</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -789,22 +789,22 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>92.94</v>
+        <v>91.0942</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>147.9886</v>
+        <v>152.914</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1.9245</v>
+        <v>1.8617</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1209.7651</v>
+        <v>1200.0995</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2.7704</v>
+        <v>297.9267</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.571</v>
+        <v>17.5246</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -814,22 +814,22 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>98.06010000000001</v>
+        <v>96.4545</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>133.5267</v>
+        <v>131.9535</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2.1374</v>
+        <v>2.1474</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1267.0219</v>
+        <v>1294.3874</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3.1194</v>
+        <v>371.4234</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.5661</v>
+        <v>19.0538</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>98.0712</v>
+        <v>96.3216</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>157.3125</v>
+        <v>159.6607</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1.9938</v>
+        <v>1.9163</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1234.8723</v>
+        <v>1243.3609</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2.872</v>
+        <v>327.25</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5886</v>
+        <v>17.639</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>99.25920000000001</v>
+        <v>96.0562</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>156.2737</v>
+        <v>139.7174</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2.2198</v>
+        <v>2.2467</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1268.6221</v>
+        <v>1319.3594</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3.2167</v>
+        <v>381.7533</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6247</v>
+        <v>20.0863</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -896,22 +896,22 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>100.9549</v>
+        <v>99.8994</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>344.2536</v>
+        <v>333.9353</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2.8545</v>
+        <v>2.9632</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1695.5191</v>
+        <v>1742.6098</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>4.0511</v>
+        <v>511.7988</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.9401</v>
+        <v>26.9317</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>99.39279999999999</v>
+        <v>99.1306</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>374.2743</v>
+        <v>380.3141</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2.745</v>
+        <v>2.7329</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>1621.0217</v>
+        <v>1614.0792</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>3.8831</v>
+        <v>479.7771</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.9241</v>
+        <v>27.4087</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>97.50020000000001</v>
+        <v>99.31489999999999</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>994.5049</v>
+        <v>390.2222</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.8991</v>
+        <v>2.7212</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>1122.6714</v>
+        <v>1550.6736</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2.7115</v>
+        <v>479.5989</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.5993000000000001</v>
+        <v>22.9237</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -971,22 +971,22 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>98.783</v>
+        <v>97.30240000000001</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>407.3229</v>
+        <v>402.8664</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>2.6207</v>
+        <v>2.6939</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1533.4764</v>
+        <v>1582.6635</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>3.7383</v>
+        <v>477.0478</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.8326</v>
+        <v>22.8053</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
@@ -996,22 +996,22 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>101.4047</v>
+        <v>98.76649999999999</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>422.8491</v>
+        <v>2453.089</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2.6683</v>
+        <v>1.5445</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1593.8764</v>
+        <v>957.1526</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>3.7635</v>
+        <v>262.366</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.9159</v>
+        <v>13.8022</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -1021,22 +1021,22 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>100.2805</v>
+        <v>97.253</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>357.4523</v>
+        <v>2790.7815</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.7994</v>
+        <v>1.4561</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>1653.2617</v>
+        <v>871.7197</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>3.9761</v>
+        <v>242.5002</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.9166</v>
+        <v>10.9121</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -1046,22 +1046,22 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>96.0346</v>
+        <v>99.2394</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>391.1991</v>
+        <v>404.2193</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.4248</v>
+        <v>2.5481</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1524.1546</v>
+        <v>1551.8785</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>3.486</v>
+        <v>410.3785</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.7267</v>
+        <v>21.5761</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>96.8211</v>
+        <v>100.2971</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>2922.1663</v>
+        <v>1085.8272</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1.5462</v>
+        <v>2.4225</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>877.0405</v>
+        <v>1357.1641</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2.2058</v>
+        <v>403.3343</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.4909</v>
+        <v>18.714</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>102.3932</v>
+        <v>99.6057</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>356.5607</v>
+        <v>703.6363</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.9219</v>
+        <v>2.373</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1668.2632</v>
+        <v>1393.2129</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>4.1074</v>
+        <v>402.7372</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>1.0251</v>
+        <v>23.0078</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
@@ -1121,22 +1121,22 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>101.774</v>
+        <v>119.286</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>377.0986</v>
+        <v>414.1782</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2.9483</v>
+        <v>3.0266</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1670.5032</v>
+        <v>1641.6072</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>4.2165</v>
+        <v>483.5746</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.9191</v>
+        <v>24.397</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1153,22 +1153,22 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>144.3436</v>
+        <v>113.3841</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>525.1502</v>
+        <v>426.2287</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>3.4203</v>
+        <v>3.7261</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>1986.9067</v>
+        <v>2183.217</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>4.8958</v>
+        <v>595.4655</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1.0594</v>
+        <v>33.4506</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>108.9962</v>
+        <v>134.723</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>447.1639</v>
+        <v>544.3173</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>3.8866</v>
+        <v>3.6679</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2123.0562</v>
+        <v>1994.263</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>5.4681</v>
+        <v>581.9422</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.3563</v>
+        <v>31.6938</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -1203,22 +1203,22 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>104.7821</v>
+        <v>104.056</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>4428.8447</v>
+        <v>4294.1125</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>2.128</v>
+        <v>2.1563</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>1184.0912</v>
+        <v>1227.6634</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>3.0303</v>
+        <v>393.9741</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.6842</v>
+        <v>16.2921</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -1228,22 +1228,22 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>121.0443</v>
+        <v>111.4064</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>4638.9933</v>
+        <v>515.7168</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>1.8045</v>
+        <v>3.3229</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>1020.6207</v>
+        <v>1929.1319</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>2.5504</v>
+        <v>519.2234</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.6111</v>
+        <v>28.1736</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
@@ -1253,22 +1253,22 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>138.5644</v>
+        <v>129.3961</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>495.5581</v>
+        <v>2884.1206</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>3.4179</v>
+        <v>2.0031</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>2018.2409</v>
+        <v>1208.4539</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>4.6923</v>
+        <v>358.0167</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.3789</v>
+        <v>16.5652</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>121.0262</v>
+        <v>108.1693</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>566.0244</v>
+        <v>1177.1668</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>3.4074</v>
+        <v>2.6337</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>1853.4082</v>
+        <v>1509.0659</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>4.6484</v>
+        <v>426.9691</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.4217</v>
+        <v>22.1082</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>112.2584</v>
+        <v>108.939</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>540.1858999999999</v>
+        <v>824.1985</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>3.2605</v>
+        <v>3.1977</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>1855.4694</v>
+        <v>1879.397</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>4.6418</v>
+        <v>548.5566</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.0506</v>
+        <v>23.1048</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
@@ -1328,22 +1328,22 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>135.3585</v>
+        <v>116.3057</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>2671.898</v>
+        <v>949.7778</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>2.1176</v>
+        <v>3.241</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1221.4806</v>
+        <v>1930.0332</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>2.9474</v>
+        <v>561.2839</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.79</v>
+        <v>26.7602</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -1353,22 +1353,22 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>117.5856</v>
+        <v>115.0147</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>785.1179</v>
+        <v>557.6106</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>3.4804</v>
+        <v>3.4161</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>2008.0525</v>
+        <v>1912.9678</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>4.9212</v>
+        <v>561.5731</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.1751</v>
+        <v>26.8952</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
@@ -1378,22 +1378,22 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>134.1585</v>
+        <v>119.4944</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>1020.4049</v>
+        <v>490.7638</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>3.3379</v>
+        <v>3.5263</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>1893.427</v>
+        <v>1982.9661</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>4.6901</v>
+        <v>597.6864</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.1744</v>
+        <v>31.0254</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
